--- a/artfynd/A 18725-2024 artfynd.xlsx
+++ b/artfynd/A 18725-2024 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>128747494</v>
       </c>
       <c r="B4" t="n">
-        <v>92748</v>
+        <v>92749</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18725-2024 artfynd.xlsx
+++ b/artfynd/A 18725-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128747497</v>
       </c>
       <c r="B2" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128747496</v>
       </c>
       <c r="B3" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128747494</v>
       </c>
       <c r="B4" t="n">
-        <v>92749</v>
+        <v>92776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128747492</v>
       </c>
       <c r="B5" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128747498</v>
       </c>
       <c r="B6" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>128747495</v>
       </c>
       <c r="B7" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 18725-2024 artfynd.xlsx
+++ b/artfynd/A 18725-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128747497</v>
       </c>
       <c r="B2" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128747496</v>
       </c>
       <c r="B3" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128747494</v>
       </c>
       <c r="B4" t="n">
-        <v>92776</v>
+        <v>92781</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128747492</v>
       </c>
       <c r="B5" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>128747495</v>
       </c>
       <c r="B7" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 18725-2024 artfynd.xlsx
+++ b/artfynd/A 18725-2024 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>128747494</v>
       </c>
       <c r="B4" t="n">
-        <v>92781</v>
+        <v>92786</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18725-2024 artfynd.xlsx
+++ b/artfynd/A 18725-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128747497</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128747496</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128747494</v>
       </c>
       <c r="B4" t="n">
-        <v>92786</v>
+        <v>92790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128747492</v>
       </c>
       <c r="B5" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128747498</v>
       </c>
       <c r="B6" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>128747495</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 18725-2024 artfynd.xlsx
+++ b/artfynd/A 18725-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128747497</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128747496</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128747494</v>
       </c>
       <c r="B4" t="n">
-        <v>92790</v>
+        <v>92795</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128747492</v>
       </c>
       <c r="B5" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128747498</v>
       </c>
       <c r="B6" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>128747495</v>
       </c>
       <c r="B7" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 18725-2024 artfynd.xlsx
+++ b/artfynd/A 18725-2024 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>128747494</v>
       </c>
       <c r="B4" t="n">
-        <v>92803</v>
+        <v>92808</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18725-2024 artfynd.xlsx
+++ b/artfynd/A 18725-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128747497</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128747496</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128747494</v>
       </c>
       <c r="B4" t="n">
-        <v>92808</v>
+        <v>92811</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128747492</v>
       </c>
       <c r="B5" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>128747495</v>
       </c>
       <c r="B7" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 18725-2024 artfynd.xlsx
+++ b/artfynd/A 18725-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128747497</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128747496</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128747494</v>
       </c>
       <c r="B4" t="n">
-        <v>92811</v>
+        <v>92818</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128747492</v>
       </c>
       <c r="B5" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128747498</v>
       </c>
       <c r="B6" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>128747495</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 18725-2024 artfynd.xlsx
+++ b/artfynd/A 18725-2024 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>128747494</v>
       </c>
       <c r="B4" t="n">
-        <v>92818</v>
+        <v>92825</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18725-2024 artfynd.xlsx
+++ b/artfynd/A 18725-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128747497</v>
+        <v>128747496</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>753543</v>
+        <v>753667</v>
       </c>
       <c r="R2" t="n">
-        <v>7128924</v>
+        <v>7129041</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128747496</v>
+        <v>128747497</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>753667</v>
+        <v>753543</v>
       </c>
       <c r="R3" t="n">
-        <v>7129041</v>
+        <v>7128924</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>128747494</v>
       </c>
       <c r="B4" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128747492</v>
       </c>
       <c r="B5" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128747498</v>
       </c>
       <c r="B6" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>128747495</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 18725-2024 artfynd.xlsx
+++ b/artfynd/A 18725-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128747496</v>
+        <v>128747497</v>
       </c>
       <c r="B2" t="n">
         <v>79041</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>753667</v>
+        <v>753543</v>
       </c>
       <c r="R2" t="n">
-        <v>7129041</v>
+        <v>7128924</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128747497</v>
+        <v>128747496</v>
       </c>
       <c r="B3" t="n">
         <v>79041</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>753543</v>
+        <v>753667</v>
       </c>
       <c r="R3" t="n">
-        <v>7128924</v>
+        <v>7129041</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 18725-2024 artfynd.xlsx
+++ b/artfynd/A 18725-2024 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>128747494</v>
       </c>
       <c r="B4" t="n">
-        <v>92827</v>
+        <v>92813</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18725-2024 artfynd.xlsx
+++ b/artfynd/A 18725-2024 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>128747494</v>
       </c>
       <c r="B4" t="n">
-        <v>92813</v>
+        <v>92814</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18725-2024 artfynd.xlsx
+++ b/artfynd/A 18725-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128747497</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128747496</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128747494</v>
       </c>
       <c r="B4" t="n">
-        <v>92814</v>
+        <v>92817</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128747492</v>
       </c>
       <c r="B5" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>128747495</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
